--- a/mdcf/Accounts-template.xlsx
+++ b/mdcf/Accounts-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\ProjectGovernance\mdcf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D92948C-DBCD-4F21-BEDC-EB5FAE08F0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0F22F3-B2D4-49DB-8F60-C26CF7556AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$1:$F$21</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -539,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="56.796875" bestFit="1" customWidth="1"/>
@@ -548,7 +561,7 @@
     <col min="6" max="6" width="41.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -568,7 +581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -587,8 +600,9 @@
       <c r="F2" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -607,8 +621,9 @@
       <c r="F3" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -627,8 +642,9 @@
       <c r="F4" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -647,8 +663,9 @@
       <c r="F5" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -667,8 +684,9 @@
       <c r="F6" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -687,8 +705,9 @@
       <c r="F7" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -707,8 +726,9 @@
       <c r="F8" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -727,8 +747,9 @@
       <c r="F9" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -747,8 +768,9 @@
       <c r="F10" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -767,8 +789,9 @@
       <c r="F11" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -787,8 +810,9 @@
       <c r="F12" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -807,8 +831,9 @@
       <c r="F13" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -827,8 +852,9 @@
       <c r="F14" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -847,8 +873,9 @@
       <c r="F15" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -867,8 +894,9 @@
       <c r="F16" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -887,8 +915,9 @@
       <c r="F17" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -907,8 +936,9 @@
       <c r="F18" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -927,8 +957,9 @@
       <c r="F19" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -947,8 +978,9 @@
       <c r="F20" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -968,17 +1000,17 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3"/>
     <row r="33" ht="15.6" x14ac:dyDescent="0.3"/>
     <row r="34" ht="15.6" x14ac:dyDescent="0.3"/>
     <row r="35" ht="15.6" x14ac:dyDescent="0.3"/>
